--- a/OMs/Sardine/Data/SA_Sardine_2025_estimates.xlsx
+++ b/OMs/Sardine/Data/SA_Sardine_2025_estimates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ClimateTestMethods\OMs\Sardine\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C77731A-47A6-4987-A970-BB5A3D6D4609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D64B7C-8586-4FAE-8A5A-379EC298C777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{136C0844-0DA2-40F9-957C-928ACC1369FC}"/>
   </bookViews>
@@ -467,10 +467,10 @@
         <v>0.54890000000000005</v>
       </c>
       <c r="C2">
-        <v>7.3599999999999999E-2</v>
+        <v>6.6199999999999995E-2</v>
       </c>
       <c r="D2">
-        <v>2.468</v>
+        <v>4.0297999999999998</v>
       </c>
       <c r="E2">
         <v>5.9186666666666665E-2</v>
@@ -487,10 +487,10 @@
         <v>0.23430000000000001</v>
       </c>
       <c r="C3">
-        <v>6.6199999999999995E-2</v>
+        <v>5.04E-2</v>
       </c>
       <c r="D3">
-        <v>4.0297999999999998</v>
+        <v>1.1196999999999999</v>
       </c>
       <c r="E3">
         <v>5.8933333333333331E-2</v>
@@ -507,10 +507,10 @@
         <v>0.15279999999999999</v>
       </c>
       <c r="C4">
-        <v>5.04E-2</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="D4">
-        <v>1.1196999999999999</v>
+        <v>1.4332</v>
       </c>
       <c r="E4">
         <v>4.36E-2</v>
@@ -527,10 +527,10 @@
         <v>8.4599999999999995E-2</v>
       </c>
       <c r="C5">
-        <v>3.4599999999999999E-2</v>
+        <v>0.50819999999999999</v>
       </c>
       <c r="D5">
-        <v>1.4332</v>
+        <v>2.4470000000000001</v>
       </c>
       <c r="E5">
         <v>3.4200000000000001E-2</v>
@@ -547,10 +547,10 @@
         <v>0.1007</v>
       </c>
       <c r="C6">
-        <v>0.50819999999999999</v>
+        <v>6.0199999999999997E-2</v>
       </c>
       <c r="D6">
-        <v>2.4470000000000001</v>
+        <v>2.6815000000000002</v>
       </c>
       <c r="E6">
         <v>5.872666666666667E-2</v>
@@ -567,10 +567,10 @@
         <v>0.1734</v>
       </c>
       <c r="C7">
-        <v>6.0199999999999997E-2</v>
+        <v>7.9200000000000007E-2</v>
       </c>
       <c r="D7">
-        <v>2.6815000000000002</v>
+        <v>5.19</v>
       </c>
       <c r="E7">
         <v>6.1233333333333334E-2</v>
@@ -587,10 +587,10 @@
         <v>0.1479</v>
       </c>
       <c r="C8">
-        <v>7.9200000000000007E-2</v>
+        <v>9.5899999999999999E-2</v>
       </c>
       <c r="D8">
-        <v>5.19</v>
+        <v>11.8238</v>
       </c>
       <c r="E8">
         <v>6.3320000000000001E-2</v>
@@ -607,10 +607,10 @@
         <v>0.14649999999999999</v>
       </c>
       <c r="C9">
-        <v>9.5899999999999999E-2</v>
+        <v>0.1125</v>
       </c>
       <c r="D9">
-        <v>11.8238</v>
+        <v>2.3826999999999998</v>
       </c>
       <c r="E9">
         <v>9.939333333333332E-2</v>
@@ -627,10 +627,10 @@
         <v>0.1018</v>
       </c>
       <c r="C10">
-        <v>0.1125</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="D10">
-        <v>2.3826999999999998</v>
+        <v>13.6546</v>
       </c>
       <c r="E10">
         <v>0.11128</v>
@@ -647,10 +647,10 @@
         <v>9.64E-2</v>
       </c>
       <c r="C11">
-        <v>0.20250000000000001</v>
+        <v>3.0078</v>
       </c>
       <c r="D11">
-        <v>13.6546</v>
+        <v>3.8208000000000002</v>
       </c>
       <c r="E11">
         <v>0.17274</v>
@@ -667,10 +667,10 @@
         <v>0.1459</v>
       </c>
       <c r="C12">
-        <v>3.0078</v>
+        <v>7.5499999999999998E-2</v>
       </c>
       <c r="D12">
-        <v>3.8208000000000002</v>
+        <v>22.406199999999998</v>
       </c>
       <c r="E12">
         <v>0.47577333333333333</v>
@@ -687,10 +687,10 @@
         <v>9.2700000000000005E-2</v>
       </c>
       <c r="C13">
-        <v>7.5499999999999998E-2</v>
+        <v>0.19769999999999999</v>
       </c>
       <c r="D13">
-        <v>22.406199999999998</v>
+        <v>14.822699999999999</v>
       </c>
       <c r="E13">
         <v>0.47014</v>
@@ -707,10 +707,10 @@
         <v>0.1051</v>
       </c>
       <c r="C14">
-        <v>0.19769999999999999</v>
+        <v>5.7995999999999999</v>
       </c>
       <c r="D14">
-        <v>14.822699999999999</v>
+        <v>6.8197000000000001</v>
       </c>
       <c r="E14">
         <v>0.33350666666666667</v>
@@ -727,10 +727,10 @@
         <v>8.4199999999999997E-2</v>
       </c>
       <c r="C15">
-        <v>5.7995999999999999</v>
+        <v>3.5817999999999999</v>
       </c>
       <c r="D15">
-        <v>6.8197000000000001</v>
+        <v>17.359100000000002</v>
       </c>
       <c r="E15">
         <v>0.60254666666666667</v>
@@ -747,10 +747,10 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="C16">
-        <v>3.5817999999999999</v>
+        <v>0.187</v>
       </c>
       <c r="D16">
-        <v>17.359100000000002</v>
+        <v>54.361499999999999</v>
       </c>
       <c r="E16">
         <v>0.77018666666666658</v>
@@ -767,10 +767,10 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="C17">
-        <v>0.187</v>
+        <v>3.9519000000000002</v>
       </c>
       <c r="D17">
-        <v>54.361499999999999</v>
+        <v>52.742100000000001</v>
       </c>
       <c r="E17">
         <v>0.81833999999999996</v>
@@ -787,10 +787,10 @@
         <v>9.1899999999999996E-2</v>
       </c>
       <c r="C18">
-        <v>3.9519000000000002</v>
+        <v>2.6648000000000001</v>
       </c>
       <c r="D18">
-        <v>52.742100000000001</v>
+        <v>46.248699999999999</v>
       </c>
       <c r="E18">
         <v>1.9667066666666666</v>
@@ -807,10 +807,10 @@
         <v>7.2599999999999998E-2</v>
       </c>
       <c r="C19">
-        <v>2.6648000000000001</v>
+        <v>0.73480000000000001</v>
       </c>
       <c r="D19">
-        <v>46.248699999999999</v>
+        <v>4.8757000000000001</v>
       </c>
       <c r="E19">
         <v>2.3502066666666668</v>
@@ -827,10 +827,10 @@
         <v>7.2700000000000001E-2</v>
       </c>
       <c r="C20">
-        <v>0.73480000000000001</v>
+        <v>0.7742</v>
       </c>
       <c r="D20">
-        <v>4.8757000000000001</v>
+        <v>3.1939000000000002</v>
       </c>
       <c r="E20">
         <v>1.99054</v>
@@ -847,10 +847,10 @@
         <v>8.72E-2</v>
       </c>
       <c r="C21">
-        <v>0.7742</v>
+        <v>2.6947000000000001</v>
       </c>
       <c r="D21">
-        <v>3.1939000000000002</v>
+        <v>5.6325000000000003</v>
       </c>
       <c r="E21">
         <v>1.3913200000000001</v>
@@ -867,10 +867,10 @@
         <v>0.1129</v>
       </c>
       <c r="C22">
-        <v>2.6947000000000001</v>
+        <v>1.2463</v>
       </c>
       <c r="D22">
-        <v>5.6325000000000003</v>
+        <v>3.0398000000000001</v>
       </c>
       <c r="E22">
         <v>0.6448666666666667</v>
@@ -887,10 +887,10 @@
         <v>0.2044</v>
       </c>
       <c r="C23">
-        <v>1.2463</v>
+        <v>1.5969</v>
       </c>
       <c r="D23">
-        <v>3.0398000000000001</v>
+        <v>4.3921999999999999</v>
       </c>
       <c r="E23">
         <v>0.41979999999999995</v>
@@ -907,10 +907,10 @@
         <v>0.1701</v>
       </c>
       <c r="C24">
-        <v>1.5969</v>
+        <v>2.2768000000000002</v>
       </c>
       <c r="D24">
-        <v>4.3921999999999999</v>
+        <v>4.4523000000000001</v>
       </c>
       <c r="E24">
         <v>0.34970000000000001</v>
@@ -927,10 +927,10 @@
         <v>0.17230000000000001</v>
       </c>
       <c r="C25">
-        <v>2.2768000000000002</v>
+        <v>0.73829999999999996</v>
       </c>
       <c r="D25">
-        <v>4.4523000000000001</v>
+        <v>15.9777</v>
       </c>
       <c r="E25">
         <v>0.28364</v>
@@ -947,10 +947,10 @@
         <v>0.16739999999999999</v>
       </c>
       <c r="C26">
-        <v>0.73829999999999996</v>
+        <v>0.2397</v>
       </c>
       <c r="D26">
-        <v>15.9777</v>
+        <v>5.1646000000000001</v>
       </c>
       <c r="E26">
         <v>0.23075999999999999</v>
@@ -967,10 +967,10 @@
         <v>0.15310000000000001</v>
       </c>
       <c r="C27">
-        <v>0.2397</v>
+        <v>0.25940000000000002</v>
       </c>
       <c r="D27">
-        <v>5.1646000000000001</v>
+        <v>5.8010999999999999</v>
       </c>
       <c r="E27">
         <v>0.33723999999999998</v>
@@ -987,10 +987,10 @@
         <v>0.10050000000000001</v>
       </c>
       <c r="C28">
-        <v>0.25940000000000002</v>
+        <v>0.1285</v>
       </c>
       <c r="D28">
-        <v>5.8010999999999999</v>
+        <v>8.8760999999999992</v>
       </c>
       <c r="E28">
         <v>0.50101333333333331</v>
@@ -1007,10 +1007,10 @@
         <v>0.1172</v>
       </c>
       <c r="C29">
-        <v>0.1285</v>
+        <v>0.84830000000000005</v>
       </c>
       <c r="D29">
-        <v>8.8760999999999992</v>
+        <v>2.0851999999999999</v>
       </c>
       <c r="E29">
         <v>0.30828</v>
@@ -1027,10 +1027,10 @@
         <v>0.1227</v>
       </c>
       <c r="C30">
-        <v>0.84830000000000005</v>
+        <v>2.0950000000000002</v>
       </c>
       <c r="D30">
-        <v>2.0851999999999999</v>
+        <v>0.94410000000000005</v>
       </c>
       <c r="E30">
         <v>0.23587333333333332</v>
@@ -1047,10 +1047,10 @@
         <v>0.1164</v>
       </c>
       <c r="C31">
-        <v>2.0950000000000002</v>
+        <v>0.7026</v>
       </c>
       <c r="D31">
-        <v>0.94410000000000005</v>
+        <v>1.7549999999999999</v>
       </c>
       <c r="E31">
         <v>0.27672666666666668</v>
@@ -1067,10 +1067,10 @@
         <v>0.1477</v>
       </c>
       <c r="C32">
-        <v>0.7026</v>
+        <v>0.84319999999999995</v>
       </c>
       <c r="D32">
-        <v>1.7549999999999999</v>
+        <v>3.2593999999999999</v>
       </c>
       <c r="E32">
         <v>0.25016666666666665</v>
@@ -1087,10 +1087,10 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="C33">
-        <v>0.84319999999999995</v>
+        <v>0.20180000000000001</v>
       </c>
       <c r="D33">
-        <v>3.2593999999999999</v>
+        <v>1.4176</v>
       </c>
       <c r="E33">
         <v>0.16021333333333332</v>
@@ -1107,10 +1107,10 @@
         <v>0.1157</v>
       </c>
       <c r="C34">
-        <v>0.20180000000000001</v>
+        <v>0.56069999999999998</v>
       </c>
       <c r="D34">
-        <v>1.4176</v>
+        <v>3.1686000000000001</v>
       </c>
       <c r="E34">
         <v>0.20099333333333333</v>
@@ -1127,10 +1127,10 @@
         <v>0.104</v>
       </c>
       <c r="C35">
-        <v>0.56069999999999998</v>
+        <v>2.7907000000000002</v>
       </c>
       <c r="D35">
-        <v>3.1686000000000001</v>
+        <v>6.6616</v>
       </c>
       <c r="E35">
         <v>0.18401333333333333</v>
@@ -1147,10 +1147,10 @@
         <v>2.76E-2</v>
       </c>
       <c r="C36">
-        <v>2.7907000000000002</v>
+        <v>0.40639999999999998</v>
       </c>
       <c r="D36">
-        <v>6.6616</v>
+        <v>2.5861000000000001</v>
       </c>
       <c r="E36">
         <v>0.28184666666666663</v>
@@ -1167,10 +1167,10 @@
         <v>7.0599999999999996E-2</v>
       </c>
       <c r="C37">
-        <v>0.40639999999999998</v>
+        <v>2.7301000000000002</v>
       </c>
       <c r="D37">
-        <v>2.5861000000000001</v>
+        <v>3.8149999999999999</v>
       </c>
       <c r="E37">
         <v>0.49311333333333335</v>
@@ -1187,10 +1187,10 @@
         <v>5.28E-2</v>
       </c>
       <c r="C38">
-        <v>2.7301000000000002</v>
+        <v>1.6855</v>
       </c>
       <c r="D38">
-        <v>3.8149999999999999</v>
+        <v>4.7432999999999996</v>
       </c>
       <c r="E38">
         <v>0.38389999999999996</v>
@@ -1206,12 +1206,6 @@
       <c r="B39">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="C39">
-        <v>1.6855</v>
-      </c>
-      <c r="D39">
-        <v>4.7432999999999996</v>
-      </c>
       <c r="E39">
         <v>0.3583466666666667</v>
       </c>
@@ -1225,9 +1219,6 @@
       </c>
       <c r="B40">
         <v>6.1499999999999999E-2</v>
-      </c>
-      <c r="D40">
-        <v>3.7452999999999999</v>
       </c>
       <c r="E40">
         <v>0.3461933333333333</v>
